--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4269998698932752</v>
+        <v>0.06938747885765723</v>
       </c>
       <c r="D2" t="n">
-        <v>0.348067899860211</v>
+        <v>0.05656103372728429</v>
       </c>
       <c r="E2" t="n">
-        <v>13.19873503875767</v>
+        <v>2.144794443798122</v>
       </c>
       <c r="F2" t="n">
-        <v>13.26999633289218</v>
+        <v>2.156374404094979</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.31696324639966</v>
+        <v>3.301506527539945</v>
       </c>
       <c r="D3" t="n">
-        <v>20.03431117014312</v>
+        <v>3.255575565148257</v>
       </c>
       <c r="E3" t="n">
-        <v>13.19873503875767</v>
+        <v>2.144794443798122</v>
       </c>
       <c r="F3" t="n">
-        <v>13.26999633289218</v>
+        <v>2.156374404094979</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.82745063252768</v>
+        <v>7.771960727785748</v>
       </c>
       <c r="D4" t="n">
-        <v>47.90185328124004</v>
+        <v>7.784051158201508</v>
       </c>
       <c r="E4" t="n">
-        <v>13.19873503875767</v>
+        <v>2.144794443798122</v>
       </c>
       <c r="F4" t="n">
-        <v>13.26999633289218</v>
+        <v>2.156374404094979</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.51787542972974</v>
+        <v>7.559154757331084</v>
       </c>
       <c r="D5" t="n">
-        <v>46.56737388689821</v>
+        <v>7.567198256620959</v>
       </c>
       <c r="E5" t="n">
-        <v>13.19873503875767</v>
+        <v>2.144794443798122</v>
       </c>
       <c r="F5" t="n">
-        <v>13.26999633289218</v>
+        <v>2.156374404094979</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.32158201621571</v>
+        <v>4.602257077635054</v>
       </c>
       <c r="D6" t="n">
-        <v>27.97418991741917</v>
+        <v>4.545805861580615</v>
       </c>
       <c r="E6" t="n">
-        <v>13.19873503875767</v>
+        <v>2.144794443798122</v>
       </c>
       <c r="F6" t="n">
-        <v>13.26999633289218</v>
+        <v>2.156374404094979</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.6032680200178</v>
+        <v>5.135531053252893</v>
       </c>
       <c r="D7" t="n">
-        <v>31.66856743324252</v>
+        <v>5.146142207901909</v>
       </c>
       <c r="E7" t="n">
-        <v>13.19873503875767</v>
+        <v>2.144794443798122</v>
       </c>
       <c r="F7" t="n">
-        <v>13.26999633289218</v>
+        <v>2.156374404094979</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.02585253687344</v>
+        <v>7.154201037241934</v>
       </c>
       <c r="D8" t="n">
-        <v>44.16526719301674</v>
+        <v>7.17685591886522</v>
       </c>
       <c r="E8" t="n">
-        <v>13.19873503875767</v>
+        <v>2.144794443798122</v>
       </c>
       <c r="F8" t="n">
-        <v>13.26999633289218</v>
+        <v>2.156374404094979</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.4897050950567</v>
+        <v>3.492077077946715</v>
       </c>
       <c r="D9" t="n">
-        <v>21.42465005933157</v>
+        <v>3.48150563464138</v>
       </c>
       <c r="E9" t="n">
-        <v>13.19873503875767</v>
+        <v>2.144794443798122</v>
       </c>
       <c r="F9" t="n">
-        <v>13.26999633289218</v>
+        <v>2.156374404094979</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.43464112429197</v>
+        <v>6.570629182697446</v>
       </c>
       <c r="D10" t="n">
-        <v>40.30082585445037</v>
+        <v>6.548884201348184</v>
       </c>
       <c r="E10" t="n">
-        <v>13.19873503875767</v>
+        <v>2.144794443798122</v>
       </c>
       <c r="F10" t="n">
-        <v>13.26999633289218</v>
+        <v>2.156374404094979</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.79629714836479</v>
+        <v>4.354398286609278</v>
       </c>
       <c r="D11" t="n">
-        <v>26.76299563064902</v>
+        <v>4.348986789980465</v>
       </c>
       <c r="E11" t="n">
-        <v>13.19873503875767</v>
+        <v>2.144794443798122</v>
       </c>
       <c r="F11" t="n">
-        <v>13.26999633289218</v>
+        <v>2.156374404094979</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>20.34542573108916</v>
+        <v>3.306131681301989</v>
       </c>
       <c r="D12" t="n">
-        <v>20.18740305790555</v>
+        <v>3.280452996909651</v>
       </c>
       <c r="E12" t="n">
-        <v>13.19873503875767</v>
+        <v>2.144794443798122</v>
       </c>
       <c r="F12" t="n">
-        <v>13.26999633289218</v>
+        <v>2.156374404094979</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>22.82677213349825</v>
+        <v>3.709350471693466</v>
       </c>
       <c r="D13" t="n">
-        <v>22.65071627464968</v>
+        <v>3.680741394630573</v>
       </c>
       <c r="E13" t="n">
-        <v>13.19873503875767</v>
+        <v>2.144794443798122</v>
       </c>
       <c r="F13" t="n">
-        <v>13.26999633289218</v>
+        <v>2.156374404094979</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
